--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/28.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/28.xlsx
@@ -426,13 +426,13 @@
         <v>-21.8444208669552</v>
       </c>
       <c r="E2">
-        <v>-15.11759705242188</v>
+        <v>-12.75423175255879</v>
       </c>
       <c r="F2">
-        <v>0.212527450349539</v>
+        <v>0.5435414077734159</v>
       </c>
       <c r="G2">
-        <v>-8.399537156180426</v>
+        <v>-7.197209916682376</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-22.22105434601407</v>
       </c>
       <c r="E3">
-        <v>-15.46927381538355</v>
+        <v>-13.93485473957254</v>
       </c>
       <c r="F3">
-        <v>0.3344034895886246</v>
+        <v>0.3219638963007845</v>
       </c>
       <c r="G3">
-        <v>-7.575694656550633</v>
+        <v>-7.178253732924509</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-22.63710861683129</v>
       </c>
       <c r="E4">
-        <v>-16.14998497126854</v>
+        <v>-13.45387645826986</v>
       </c>
       <c r="F4">
-        <v>0.3806048531123643</v>
+        <v>0.718849629595278</v>
       </c>
       <c r="G4">
-        <v>-7.433394167090601</v>
+        <v>-6.797405263541213</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-23.0051715916706</v>
       </c>
       <c r="E5">
-        <v>-15.8394765655106</v>
+        <v>-15.32360186350481</v>
       </c>
       <c r="F5">
-        <v>0.8526226814733702</v>
+        <v>0.7590221351614429</v>
       </c>
       <c r="G5">
-        <v>-7.421784083884376</v>
+        <v>-7.502617674316761</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-23.28222726160499</v>
       </c>
       <c r="E6">
-        <v>-16.85430759062953</v>
+        <v>-15.67029277658404</v>
       </c>
       <c r="F6">
-        <v>0.4062892128035658</v>
+        <v>0.8387375870676449</v>
       </c>
       <c r="G6">
-        <v>-7.693245507559075</v>
+        <v>-6.932816507734023</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-23.41843614681792</v>
       </c>
       <c r="E7">
-        <v>-17.85276365373672</v>
+        <v>-15.81804782650631</v>
       </c>
       <c r="F7">
-        <v>0.688114713849208</v>
+        <v>0.6766517657292684</v>
       </c>
       <c r="G7">
-        <v>-7.312142126169254</v>
+        <v>-6.473574319980784</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-23.37564003705487</v>
       </c>
       <c r="E8">
-        <v>-18.08067722206876</v>
+        <v>-15.82533414118465</v>
       </c>
       <c r="F8">
-        <v>0.5827438951109024</v>
+        <v>0.7759937265099991</v>
       </c>
       <c r="G8">
-        <v>-6.9948759944132</v>
+        <v>-5.618894088652681</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-23.11781575059328</v>
       </c>
       <c r="E9">
-        <v>-18.77694821464411</v>
+        <v>-17.01458839965701</v>
       </c>
       <c r="F9">
-        <v>0.2111730696459618</v>
+        <v>0.8443837392851263</v>
       </c>
       <c r="G9">
-        <v>-6.848976941951979</v>
+        <v>-6.070823281309669</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-22.64164779309875</v>
       </c>
       <c r="E10">
-        <v>-19.81026447066235</v>
+        <v>-18.14318374879664</v>
       </c>
       <c r="F10">
-        <v>0.6126529285563814</v>
+        <v>0.7853542781616335</v>
       </c>
       <c r="G10">
-        <v>-6.347081685470771</v>
+        <v>-4.91491982190882</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-21.94831259449331</v>
       </c>
       <c r="E11">
-        <v>-20.19787467487489</v>
+        <v>-18.68527378683283</v>
       </c>
       <c r="F11">
-        <v>0.6609467481395925</v>
+        <v>0.8616684535119408</v>
       </c>
       <c r="G11">
-        <v>-5.904726590513355</v>
+        <v>-4.456631071270892</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-21.0805421281699</v>
       </c>
       <c r="E12">
-        <v>-21.23551109509644</v>
+        <v>-19.09237001470037</v>
       </c>
       <c r="F12">
-        <v>0.9821544922491289</v>
+        <v>1.136103260589806</v>
       </c>
       <c r="G12">
-        <v>-5.730419746779648</v>
+        <v>-3.310020313198777</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-20.07714609429567</v>
       </c>
       <c r="E13">
-        <v>-21.8490740383957</v>
+        <v>-20.00137965920806</v>
       </c>
       <c r="F13">
-        <v>1.181181357915349</v>
+        <v>1.110818173986754</v>
       </c>
       <c r="G13">
-        <v>-4.69402367080095</v>
+        <v>-2.985689477261918</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-19.01640071878351</v>
       </c>
       <c r="E14">
-        <v>-22.52817758600797</v>
+        <v>-20.83634875369033</v>
       </c>
       <c r="F14">
-        <v>1.053485209304194</v>
+        <v>1.459078740736916</v>
       </c>
       <c r="G14">
-        <v>-4.231941034975017</v>
+        <v>-3.773496688696743</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-17.9655420717755</v>
       </c>
       <c r="E15">
-        <v>-23.40088245439616</v>
+        <v>-21.29268760791728</v>
       </c>
       <c r="F15">
-        <v>1.491728013550856</v>
+        <v>1.607344908694389</v>
       </c>
       <c r="G15">
-        <v>-3.659243141045416</v>
+        <v>-2.23541392060581</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-16.99565432252158</v>
       </c>
       <c r="E16">
-        <v>-23.64689180486285</v>
+        <v>-22.62319402763691</v>
       </c>
       <c r="F16">
-        <v>1.787986988222877</v>
+        <v>2.043024744196789</v>
       </c>
       <c r="G16">
-        <v>-4.048212378636545</v>
+        <v>-2.225753748722217</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-16.17401563959941</v>
       </c>
       <c r="E17">
-        <v>-25.48122265725385</v>
+        <v>-23.24462745876149</v>
       </c>
       <c r="F17">
-        <v>2.095740388976143</v>
+        <v>2.173661597087882</v>
       </c>
       <c r="G17">
-        <v>-3.780356139054113</v>
+        <v>-1.776535892861892</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-15.54038525203703</v>
       </c>
       <c r="E18">
-        <v>-25.60633080866376</v>
+        <v>-24.70942124670457</v>
       </c>
       <c r="F18">
-        <v>2.305304088005974</v>
+        <v>2.561549603653167</v>
       </c>
       <c r="G18">
-        <v>-3.199186559089517</v>
+        <v>-1.806185138711605</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-15.13010619001227</v>
       </c>
       <c r="E19">
-        <v>-26.13808686901445</v>
+        <v>-24.67302137263092</v>
       </c>
       <c r="F19">
-        <v>2.805785448694573</v>
+        <v>2.925428209415712</v>
       </c>
       <c r="G19">
-        <v>-3.296778131041692</v>
+        <v>-1.598186873024735</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-14.9392294981855</v>
       </c>
       <c r="E20">
-        <v>-26.6918965977825</v>
+        <v>-25.99784908594492</v>
       </c>
       <c r="F20">
-        <v>2.929853348081466</v>
+        <v>3.025876040679179</v>
       </c>
       <c r="G20">
-        <v>-3.230587083529504</v>
+        <v>-1.436834193986197</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-14.96584033657006</v>
       </c>
       <c r="E21">
-        <v>-27.05393903774773</v>
+        <v>-25.20932854935932</v>
       </c>
       <c r="F21">
-        <v>2.881528050536949</v>
+        <v>3.793330274881226</v>
       </c>
       <c r="G21">
-        <v>-3.069628359410139</v>
+        <v>-2.035920446409329</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-15.17376644958119</v>
       </c>
       <c r="E22">
-        <v>-27.70041040166073</v>
+        <v>-25.69477643450757</v>
       </c>
       <c r="F22">
-        <v>3.512608159216113</v>
+        <v>3.54505531038377</v>
       </c>
       <c r="G22">
-        <v>-3.166544580072303</v>
+        <v>-2.546631685661616</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-15.52415752835783</v>
       </c>
       <c r="E23">
-        <v>-28.19480202297413</v>
+        <v>-26.08890311281715</v>
       </c>
       <c r="F23">
-        <v>3.516625741119691</v>
+        <v>4.308654322693187</v>
       </c>
       <c r="G23">
-        <v>-3.746740859648353</v>
+        <v>-2.65426745277994</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-15.9675417181675</v>
       </c>
       <c r="E24">
-        <v>-28.32588323160016</v>
+        <v>-27.54310027158227</v>
       </c>
       <c r="F24">
-        <v>3.760472253481781</v>
+        <v>4.125711038519722</v>
       </c>
       <c r="G24">
-        <v>-4.17537374334549</v>
+        <v>-2.449424136991996</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-16.44079234937291</v>
       </c>
       <c r="E25">
-        <v>-28.96818387095209</v>
+        <v>-27.86533742502008</v>
       </c>
       <c r="F25">
-        <v>4.055144076210038</v>
+        <v>4.398527215692517</v>
       </c>
       <c r="G25">
-        <v>-3.933349690605992</v>
+        <v>-3.037112181123417</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-16.89211283949698</v>
       </c>
       <c r="E26">
-        <v>-29.20510457408539</v>
+        <v>-27.07897244206213</v>
       </c>
       <c r="F26">
-        <v>4.077702177323074</v>
+        <v>4.55351641349111</v>
       </c>
       <c r="G26">
-        <v>-4.48752839278891</v>
+        <v>-3.330568869361033</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-17.26110237842048</v>
       </c>
       <c r="E27">
-        <v>-29.53652547281075</v>
+        <v>-26.81503033452506</v>
       </c>
       <c r="F27">
-        <v>4.004679934031492</v>
+        <v>4.477202238140803</v>
       </c>
       <c r="G27">
-        <v>-4.220330951768793</v>
+        <v>-2.811101237157373</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-17.51208677984382</v>
       </c>
       <c r="E28">
-        <v>-29.07603853639277</v>
+        <v>-27.17305148957148</v>
       </c>
       <c r="F28">
-        <v>4.024471288019178</v>
+        <v>4.473076968474861</v>
       </c>
       <c r="G28">
-        <v>-4.092706110684349</v>
+        <v>-3.160281027912002</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-17.6096387842517</v>
       </c>
       <c r="E29">
-        <v>-28.17412501065511</v>
+        <v>-27.73022587452723</v>
       </c>
       <c r="F29">
-        <v>4.02555479258204</v>
+        <v>4.582283956655531</v>
       </c>
       <c r="G29">
-        <v>-3.726437283856003</v>
+        <v>-3.880927201991632</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-17.54653622625401</v>
       </c>
       <c r="E30">
-        <v>-28.10477143122764</v>
+        <v>-26.51359699067849</v>
       </c>
       <c r="F30">
-        <v>4.11526201210081</v>
+        <v>4.34526650516212</v>
       </c>
       <c r="G30">
-        <v>-3.826548180963564</v>
+        <v>-3.259971485736075</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-17.32704482443823</v>
       </c>
       <c r="E31">
-        <v>-28.31318991895666</v>
+        <v>-26.67811645137716</v>
       </c>
       <c r="F31">
-        <v>3.913895836889083</v>
+        <v>4.431658598334886</v>
       </c>
       <c r="G31">
-        <v>-3.789281369827988</v>
+        <v>-3.229842210783168</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-16.96618160667188</v>
       </c>
       <c r="E32">
-        <v>-27.27950232806979</v>
+        <v>-26.33948169355758</v>
       </c>
       <c r="F32">
-        <v>3.920375326713781</v>
+        <v>4.044179805266584</v>
       </c>
       <c r="G32">
-        <v>-3.750233485192284</v>
+        <v>-2.696983421873156</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-16.50036190414222</v>
       </c>
       <c r="E33">
-        <v>-27.32090163744791</v>
+        <v>-27.29128994591176</v>
       </c>
       <c r="F33">
-        <v>3.290037435227525</v>
+        <v>4.115780570094961</v>
       </c>
       <c r="G33">
-        <v>-3.462530525101922</v>
+        <v>-2.715443023800133</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-15.96127272977072</v>
       </c>
       <c r="E34">
-        <v>-27.0527435206097</v>
+        <v>-26.77497145345321</v>
       </c>
       <c r="F34">
-        <v>3.846904108289881</v>
+        <v>3.97951910253886</v>
       </c>
       <c r="G34">
-        <v>-3.156861234369935</v>
+        <v>-2.921163634155983</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-15.393804397974</v>
       </c>
       <c r="E35">
-        <v>-26.51916248523392</v>
+        <v>-25.41113546503714</v>
       </c>
       <c r="F35">
-        <v>3.713638017262303</v>
+        <v>4.102369301843638</v>
       </c>
       <c r="G35">
-        <v>-3.576171621828484</v>
+        <v>-1.948839856544339</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-14.82526782025984</v>
       </c>
       <c r="E36">
-        <v>-26.57963119865834</v>
+        <v>-25.00097798874041</v>
       </c>
       <c r="F36">
-        <v>3.512508755127777</v>
+        <v>3.931389299701403</v>
       </c>
       <c r="G36">
-        <v>-2.910540093520462</v>
+        <v>-1.980518466809625</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-14.29489105151284</v>
       </c>
       <c r="E37">
-        <v>-26.35956094730759</v>
+        <v>-25.46301366326901</v>
       </c>
       <c r="F37">
-        <v>3.800449264340885</v>
+        <v>4.192823708759732</v>
       </c>
       <c r="G37">
-        <v>-2.125675957070049</v>
+        <v>-1.730701389870682</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-13.82440334432662</v>
       </c>
       <c r="E38">
-        <v>-25.84335113822523</v>
+        <v>-25.00199689539214</v>
       </c>
       <c r="F38">
-        <v>3.589762299112859</v>
+        <v>3.962340419339604</v>
       </c>
       <c r="G38">
-        <v>-2.295036845768085</v>
+        <v>-1.322173449233539</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-13.43399951909199</v>
       </c>
       <c r="E39">
-        <v>-25.96604108451504</v>
+        <v>-23.82635522978683</v>
       </c>
       <c r="F39">
-        <v>3.796234530995442</v>
+        <v>3.836927251290564</v>
       </c>
       <c r="G39">
-        <v>-2.285770628803664</v>
+        <v>-1.016457810864002</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-13.14036491712757</v>
       </c>
       <c r="E40">
-        <v>-24.66827553187088</v>
+        <v>-24.52019443182006</v>
       </c>
       <c r="F40">
-        <v>3.492530190107058</v>
+        <v>3.621844968623284</v>
       </c>
       <c r="G40">
-        <v>-1.846947885936651</v>
+        <v>-1.368517776237796</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-12.94476355973536</v>
       </c>
       <c r="E41">
-        <v>-24.32062005382802</v>
+        <v>-23.48708195713217</v>
       </c>
       <c r="F41">
-        <v>3.592262311934508</v>
+        <v>3.8321442579068</v>
       </c>
       <c r="G41">
-        <v>-2.013143893099143</v>
+        <v>-0.5552822645158294</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-12.85125715983542</v>
       </c>
       <c r="E42">
-        <v>-23.05831245266391</v>
+        <v>-23.94365176353351</v>
       </c>
       <c r="F42">
-        <v>3.557830392469744</v>
+        <v>3.523584027303206</v>
       </c>
       <c r="G42">
-        <v>-1.413431947569089</v>
+        <v>-1.07361106905398</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-12.84288059403079</v>
       </c>
       <c r="E43">
-        <v>-24.10109774783219</v>
+        <v>-22.69201324713147</v>
       </c>
       <c r="F43">
-        <v>3.745389339811608</v>
+        <v>3.777856371796931</v>
       </c>
       <c r="G43">
-        <v>-1.715436464389103</v>
+        <v>-0.1957768822242141</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-12.9108258962879</v>
       </c>
       <c r="E44">
-        <v>-23.71788016340709</v>
+        <v>-22.61818100691042</v>
       </c>
       <c r="F44">
-        <v>3.631757212965183</v>
+        <v>3.802248478339766</v>
       </c>
       <c r="G44">
-        <v>-1.422281035795561</v>
+        <v>-0.2593360460326816</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-13.02924540841106</v>
       </c>
       <c r="E45">
-        <v>-22.86183102241911</v>
+        <v>-21.57709388949501</v>
       </c>
       <c r="F45">
-        <v>3.360097436686696</v>
+        <v>3.848211272051499</v>
       </c>
       <c r="G45">
-        <v>-1.834106279789818</v>
+        <v>-0.9163833297573734</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-13.1793487094813</v>
       </c>
       <c r="E46">
-        <v>-22.95963700403678</v>
+        <v>-20.35437873657997</v>
       </c>
       <c r="F46">
-        <v>3.338591362175215</v>
+        <v>3.594522098209345</v>
       </c>
       <c r="G46">
-        <v>-1.675408658273775</v>
+        <v>-0.6374069677085297</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-13.34174598495233</v>
       </c>
       <c r="E47">
-        <v>-22.17056399362224</v>
+        <v>-21.3724566775624</v>
       </c>
       <c r="F47">
-        <v>3.330685423682897</v>
+        <v>3.64169265159436</v>
       </c>
       <c r="G47">
-        <v>-1.657389358903522</v>
+        <v>0.05929734103109159</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-13.49262472393045</v>
       </c>
       <c r="E48">
-        <v>-21.39629003626477</v>
+        <v>-20.29655918045004</v>
       </c>
       <c r="F48">
-        <v>3.393228819329065</v>
+        <v>3.747261450141935</v>
       </c>
       <c r="G48">
-        <v>-1.565905743471302</v>
+        <v>-0.4159678871322193</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-13.62210281518432</v>
       </c>
       <c r="E49">
-        <v>-21.57347563876289</v>
+        <v>-19.93792668141258</v>
       </c>
       <c r="F49">
-        <v>3.12447826936921</v>
+        <v>3.350392284195497</v>
       </c>
       <c r="G49">
-        <v>-2.550680482856145</v>
+        <v>-0.5622675156036916</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-13.71278899913286</v>
       </c>
       <c r="E50">
-        <v>-20.76660572549821</v>
+        <v>-19.81806250290355</v>
       </c>
       <c r="F50">
-        <v>3.189374228439329</v>
+        <v>3.473896893748487</v>
       </c>
       <c r="G50">
-        <v>-1.880261905698337</v>
+        <v>-0.7422420133006304</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-13.76396823064275</v>
       </c>
       <c r="E51">
-        <v>-21.23140376917148</v>
+        <v>-19.21298591989467</v>
       </c>
       <c r="F51">
-        <v>3.196524695860294</v>
+        <v>3.355031141651174</v>
       </c>
       <c r="G51">
-        <v>-2.611591210233195</v>
+        <v>-0.7317674472143764</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-13.76894130926159</v>
       </c>
       <c r="E52">
-        <v>-20.06012302403556</v>
+        <v>-19.90183927204546</v>
       </c>
       <c r="F52">
-        <v>3.383207230489996</v>
+        <v>3.192992537254757</v>
       </c>
       <c r="G52">
-        <v>-2.699052512835201</v>
+        <v>-0.5593707882568293</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-13.73641774376721</v>
       </c>
       <c r="E53">
-        <v>-19.45285013113296</v>
+        <v>-18.67071474289817</v>
       </c>
       <c r="F53">
-        <v>3.167172325309497</v>
+        <v>3.293549713015395</v>
       </c>
       <c r="G53">
-        <v>-2.685091942296094</v>
+        <v>-1.051824368860036</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-13.67600636969365</v>
       </c>
       <c r="E54">
-        <v>-19.83536580208687</v>
+        <v>-18.50213324101463</v>
       </c>
       <c r="F54">
-        <v>3.368495425416278</v>
+        <v>3.371936463607506</v>
       </c>
       <c r="G54">
-        <v>-2.829256268894737</v>
+        <v>-1.210459090010833</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-13.59485994474652</v>
       </c>
       <c r="E55">
-        <v>-19.2482491469924</v>
+        <v>-18.12518759309015</v>
       </c>
       <c r="F55">
-        <v>3.459846125862201</v>
+        <v>3.672686846337506</v>
       </c>
       <c r="G55">
-        <v>-3.279900969882488</v>
+        <v>-1.61070073516318</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-13.51376478597774</v>
       </c>
       <c r="E56">
-        <v>-18.96359379934425</v>
+        <v>-18.01214329643668</v>
       </c>
       <c r="F56">
-        <v>3.302259167888429</v>
+        <v>3.453911701788546</v>
       </c>
       <c r="G56">
-        <v>-2.843147317977519</v>
+        <v>-1.336829234335893</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-13.44057420130889</v>
       </c>
       <c r="E57">
-        <v>-17.936766846579</v>
+        <v>-16.77823828424868</v>
       </c>
       <c r="F57">
-        <v>3.423273705028603</v>
+        <v>3.385064430207073</v>
       </c>
       <c r="G57">
-        <v>-3.339278914674856</v>
+        <v>-1.973755022272894</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-13.39379384902114</v>
       </c>
       <c r="E58">
-        <v>-18.58289857494143</v>
+        <v>-17.2389878721591</v>
       </c>
       <c r="F58">
-        <v>3.616429102543781</v>
+        <v>3.179399028174818</v>
       </c>
       <c r="G58">
-        <v>-2.944651954757112</v>
+        <v>-1.98962577758816</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-13.377821965397</v>
       </c>
       <c r="E59">
-        <v>-18.10264937795398</v>
+        <v>-16.44495618270617</v>
       </c>
       <c r="F59">
-        <v>3.523020737469303</v>
+        <v>3.668460515848423</v>
       </c>
       <c r="G59">
-        <v>-3.945658298921002</v>
+        <v>-2.460362179453748</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-13.40452426207787</v>
       </c>
       <c r="E60">
-        <v>-17.58001819272874</v>
+        <v>-16.29072994342694</v>
       </c>
       <c r="F60">
-        <v>3.273769956171348</v>
+        <v>3.767571362123773</v>
       </c>
       <c r="G60">
-        <v>-3.792826964100548</v>
+        <v>-1.793982467853851</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-13.47558341321329</v>
       </c>
       <c r="E61">
-        <v>-17.92210364774217</v>
+        <v>-16.80617896887601</v>
       </c>
       <c r="F61">
-        <v>3.205280539307885</v>
+        <v>3.685456958219063</v>
       </c>
       <c r="G61">
-        <v>-4.366167103864767</v>
+        <v>-2.780505175283429</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.58817442132215</v>
       </c>
       <c r="E62">
-        <v>-17.27397033386836</v>
+        <v>-16.08030081323851</v>
       </c>
       <c r="F62">
-        <v>3.229241894801264</v>
+        <v>3.852088031496601</v>
       </c>
       <c r="G62">
-        <v>-4.8144414542464</v>
+        <v>-2.43986659202012</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.74296568558343</v>
       </c>
       <c r="E63">
-        <v>-17.48561762356485</v>
+        <v>-16.48829820743358</v>
       </c>
       <c r="F63">
-        <v>3.328201978209304</v>
+        <v>3.454518066727395</v>
       </c>
       <c r="G63">
-        <v>-4.656938939670034</v>
+        <v>-3.179333217490508</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.92584044919335</v>
       </c>
       <c r="E64">
-        <v>-16.72508305634665</v>
+        <v>-15.74812818782788</v>
       </c>
       <c r="F64">
-        <v>3.320025991943673</v>
+        <v>3.530552253895556</v>
       </c>
       <c r="G64">
-        <v>-4.072326392344596</v>
+        <v>-3.220556130545512</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-14.13346719638106</v>
       </c>
       <c r="E65">
-        <v>-16.83026592212281</v>
+        <v>-15.21568379942802</v>
       </c>
       <c r="F65">
-        <v>3.321005122213782</v>
+        <v>3.557580225514098</v>
       </c>
       <c r="G65">
-        <v>-4.765859198457595</v>
+        <v>-2.712264900082432</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-14.34941355491799</v>
       </c>
       <c r="E66">
-        <v>-16.83752053748309</v>
+        <v>-15.46194674443914</v>
       </c>
       <c r="F66">
-        <v>3.339128144252229</v>
+        <v>3.671242173587024</v>
       </c>
       <c r="G66">
-        <v>-4.05627355702467</v>
+        <v>-3.079669244030748</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-14.56860358555308</v>
       </c>
       <c r="E67">
-        <v>-17.20268762451362</v>
+        <v>-15.72083507498365</v>
       </c>
       <c r="F67">
-        <v>2.940792768002837</v>
+        <v>3.535199395025261</v>
       </c>
       <c r="G67">
-        <v>-4.571708944761498</v>
+        <v>-3.112440334323994</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-14.77712372467849</v>
       </c>
       <c r="E68">
-        <v>-16.98197432985377</v>
+        <v>-15.69284457714224</v>
       </c>
       <c r="F68">
-        <v>3.003324566505366</v>
+        <v>3.36176742537074</v>
       </c>
       <c r="G68">
-        <v>-4.957705312458361</v>
+        <v>-2.765713657813965</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-14.9666312465514</v>
       </c>
       <c r="E69">
-        <v>-16.57256858024232</v>
+        <v>-16.13473307081071</v>
       </c>
       <c r="F69">
-        <v>2.933354028725697</v>
+        <v>3.462147330507178</v>
       </c>
       <c r="G69">
-        <v>-4.177307101940425</v>
+        <v>-3.341735339464995</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-15.13109345142938</v>
       </c>
       <c r="E70">
-        <v>-17.44934454676341</v>
+        <v>-15.51825379025051</v>
       </c>
       <c r="F70">
-        <v>3.064148271423322</v>
+        <v>3.545598719400006</v>
       </c>
       <c r="G70">
-        <v>-5.203476902748315</v>
+        <v>-3.787695618514677</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-15.25687002477407</v>
       </c>
       <c r="E71">
-        <v>-17.12618811310204</v>
+        <v>-15.4012289649443</v>
       </c>
       <c r="F71">
-        <v>3.137392517178855</v>
+        <v>3.211120529497622</v>
       </c>
       <c r="G71">
-        <v>-4.37278488439777</v>
+        <v>-2.830537450018435</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-15.34607188707736</v>
       </c>
       <c r="E72">
-        <v>-16.04330318059585</v>
+        <v>-15.44296790987299</v>
       </c>
       <c r="F72">
-        <v>3.020312725201978</v>
+        <v>2.938102230678544</v>
       </c>
       <c r="G72">
-        <v>-4.689696787781123</v>
+        <v>-3.048076707949483</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-15.39008913870905</v>
       </c>
       <c r="E73">
-        <v>-16.76052289393068</v>
+        <v>-15.86316954151873</v>
       </c>
       <c r="F73">
-        <v>2.985357277538645</v>
+        <v>3.00557772584098</v>
       </c>
       <c r="G73">
-        <v>-4.372993448766745</v>
+        <v>-3.470310307119209</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-15.39454775839101</v>
       </c>
       <c r="E74">
-        <v>-17.74054806782665</v>
+        <v>-16.39794609403254</v>
       </c>
       <c r="F74">
-        <v>2.665127006964412</v>
+        <v>2.943325915520598</v>
       </c>
       <c r="G74">
-        <v>-3.927298013360204</v>
+        <v>-3.069231093945426</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-15.35448845095536</v>
       </c>
       <c r="E75">
-        <v>-17.11692285528235</v>
+        <v>-15.93437073834133</v>
       </c>
       <c r="F75">
-        <v>2.527334716447936</v>
+        <v>2.847462269464222</v>
       </c>
       <c r="G75">
-        <v>-4.293540355824236</v>
+        <v>-2.967680109528283</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-15.27864297103644</v>
       </c>
       <c r="E76">
-        <v>-17.81499618051275</v>
+        <v>-16.10048875036471</v>
       </c>
       <c r="F76">
-        <v>2.30497439777966</v>
+        <v>2.495015133860311</v>
       </c>
       <c r="G76">
-        <v>-4.725940640345064</v>
+        <v>-3.097820965222572</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-15.17077111308308</v>
       </c>
       <c r="E77">
-        <v>-17.33312126135655</v>
+        <v>-16.28658186123591</v>
       </c>
       <c r="F77">
-        <v>2.379880348545207</v>
+        <v>2.838525841922821</v>
       </c>
       <c r="G77">
-        <v>-3.609767037961008</v>
+        <v>-3.143191991838284</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-15.03476540119645</v>
       </c>
       <c r="E78">
-        <v>-18.29739640265384</v>
+        <v>-17.31524737444827</v>
       </c>
       <c r="F78">
-        <v>2.551721852786354</v>
+        <v>2.792886111498179</v>
       </c>
       <c r="G78">
-        <v>-3.747058672020124</v>
+        <v>-2.795362903663678</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-14.88293671387551</v>
       </c>
       <c r="E79">
-        <v>-18.40004332298571</v>
+        <v>-17.61368286850177</v>
       </c>
       <c r="F79">
-        <v>2.397276064003997</v>
+        <v>2.257480781107553</v>
       </c>
       <c r="G79">
-        <v>-4.199732737423448</v>
+        <v>-2.47893102938352</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-14.71742528911865</v>
       </c>
       <c r="E80">
-        <v>-18.14107347990906</v>
+        <v>-17.63718564860157</v>
       </c>
       <c r="F80">
-        <v>2.111499250447001</v>
+        <v>2.237816995699898</v>
       </c>
       <c r="G80">
-        <v>-3.4057612901945</v>
+        <v>-2.340235724015754</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-14.55012815835337</v>
       </c>
       <c r="E81">
-        <v>-19.39716348626063</v>
+        <v>-17.90303424369587</v>
       </c>
       <c r="F81">
-        <v>1.786045295030715</v>
+        <v>2.082720110138941</v>
       </c>
       <c r="G81">
-        <v>-3.711877504574288</v>
+        <v>-2.619480240253278</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-14.37845260212505</v>
       </c>
       <c r="E82">
-        <v>-19.3181506717748</v>
+        <v>-18.52209475444044</v>
       </c>
       <c r="F82">
-        <v>1.911410417770392</v>
+        <v>2.266639211112904</v>
       </c>
       <c r="G82">
-        <v>-3.321441695309262</v>
+        <v>-1.260517849110153</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-14.21075512615076</v>
       </c>
       <c r="E83">
-        <v>-20.23700521877516</v>
+        <v>-19.36557285158313</v>
       </c>
       <c r="F83">
-        <v>1.625065344175076</v>
+        <v>1.91407279060299</v>
       </c>
       <c r="G83">
-        <v>-2.95143195202154</v>
+        <v>-1.751140698030142</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-14.04130290466029</v>
       </c>
       <c r="E84">
-        <v>-20.96845339744209</v>
+        <v>-19.43626233084286</v>
       </c>
       <c r="F84">
-        <v>1.608930403903347</v>
+        <v>2.102849438026969</v>
       </c>
       <c r="G84">
-        <v>-3.022615302206949</v>
+        <v>-1.391036106995919</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-13.87135919452314</v>
       </c>
       <c r="E85">
-        <v>-21.88411084179304</v>
+        <v>-20.46735963459734</v>
       </c>
       <c r="F85">
-        <v>1.459411744432842</v>
+        <v>1.711086328751387</v>
       </c>
       <c r="G85">
-        <v>-2.956136237232844</v>
+        <v>-1.681721868617165</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-13.69934939934021</v>
       </c>
       <c r="E86">
-        <v>-22.80473149365639</v>
+        <v>-22.06493733739333</v>
       </c>
       <c r="F86">
-        <v>1.295070278656642</v>
+        <v>1.445871250866681</v>
       </c>
       <c r="G86">
-        <v>-2.452069262877874</v>
+        <v>-1.43940979841575</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-13.51932401364769</v>
       </c>
       <c r="E87">
-        <v>-24.08375822085682</v>
+        <v>-23.1958648506469</v>
       </c>
       <c r="F87">
-        <v>1.126840456291702</v>
+        <v>1.323829538147035</v>
       </c>
       <c r="G87">
-        <v>-2.570037242624263</v>
+        <v>-1.406115641927299</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-13.33377741714411</v>
       </c>
       <c r="E88">
-        <v>-25.50242044408376</v>
+        <v>-23.37830801146792</v>
       </c>
       <c r="F88">
-        <v>1.053906019944816</v>
+        <v>1.194471684525864</v>
       </c>
       <c r="G88">
-        <v>-2.583448262603851</v>
+        <v>-1.419976896100228</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-13.13546805657815</v>
       </c>
       <c r="E89">
-        <v>-26.54917268248275</v>
+        <v>-25.61257104584633</v>
       </c>
       <c r="F89">
-        <v>1.107658780712476</v>
+        <v>1.118071358965666</v>
       </c>
       <c r="G89">
-        <v>-2.017679340487944</v>
+        <v>-0.7831669772571008</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-12.93087780218781</v>
       </c>
       <c r="E90">
-        <v>-28.69202846901634</v>
+        <v>-26.91119248007794</v>
       </c>
       <c r="F90">
-        <v>0.5186166609905816</v>
+        <v>0.9640629481719877</v>
       </c>
       <c r="G90">
-        <v>-1.771033766175623</v>
+        <v>-1.063424520429642</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-12.71428632480193</v>
       </c>
       <c r="E91">
-        <v>-29.86003286320771</v>
+        <v>-29.39452158487822</v>
       </c>
       <c r="F91">
-        <v>0.378453582967294</v>
+        <v>0.6679920129004023</v>
       </c>
       <c r="G91">
-        <v>-1.955623164354306</v>
+        <v>-1.018278610910601</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-12.49548610639989</v>
       </c>
       <c r="E92">
-        <v>-30.35068170075377</v>
+        <v>-29.99990610411963</v>
       </c>
       <c r="F92">
-        <v>0.3836383345414161</v>
+        <v>0.5979775716483854</v>
       </c>
       <c r="G92">
-        <v>-1.668966336654353</v>
+        <v>-1.513973215596755</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-12.28002772558699</v>
       </c>
       <c r="E93">
-        <v>-32.49826068567735</v>
+        <v>-32.21471481416108</v>
       </c>
       <c r="F93">
-        <v>0.4656127443550523</v>
+        <v>0.06238503022472582</v>
       </c>
       <c r="G93">
-        <v>-1.955086855976944</v>
+        <v>-1.446845283696953</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-12.073864689527</v>
       </c>
       <c r="E94">
-        <v>-35.16799989452937</v>
+        <v>-33.33217011724184</v>
       </c>
       <c r="F94">
-        <v>0.176363414645521</v>
+        <v>0.4959094537450415</v>
       </c>
       <c r="G94">
-        <v>-1.823277485330862</v>
+        <v>-1.089097801086691</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-11.89216341014397</v>
       </c>
       <c r="E95">
-        <v>-37.46934547862041</v>
+        <v>-35.6830685281618</v>
       </c>
       <c r="F95">
-        <v>-0.01011368486828692</v>
+        <v>-0.1406345663229882</v>
       </c>
       <c r="G95">
-        <v>-2.58031979706924</v>
+        <v>-1.718498719012929</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.74404534595372</v>
       </c>
       <c r="E96">
-        <v>-39.34487412329619</v>
+        <v>-37.6631686946227</v>
       </c>
       <c r="F96">
-        <v>-0.4359657695038736</v>
+        <v>-0.2699311207563518</v>
       </c>
       <c r="G96">
-        <v>-2.289101037616171</v>
+        <v>-1.755179563588053</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.64194453133331</v>
       </c>
       <c r="E97">
-        <v>-41.40167984673602</v>
+        <v>-39.65713957696911</v>
       </c>
       <c r="F97">
-        <v>-0.4363965205533293</v>
+        <v>-0.1259327016581026</v>
       </c>
       <c r="G97">
-        <v>-2.481172268713607</v>
+        <v>-1.649073268508872</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.59727024239798</v>
       </c>
       <c r="E98">
-        <v>-43.70902565888722</v>
+        <v>-42.71448446155966</v>
       </c>
       <c r="F98">
-        <v>-0.5678816216648892</v>
+        <v>-0.5407608728972334</v>
       </c>
       <c r="G98">
-        <v>-2.541775115355505</v>
+        <v>-1.649890973257073</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.6106839492467</v>
       </c>
       <c r="E99">
-        <v>-46.27213062604362</v>
+        <v>-45.84364415120085</v>
       </c>
       <c r="F99">
-        <v>-0.6230542041609475</v>
+        <v>-0.8666298403823225</v>
       </c>
       <c r="G99">
-        <v>-2.883843854291779</v>
+        <v>-1.821777808201572</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.70211296049719</v>
       </c>
       <c r="E100">
-        <v>-48.38835219270109</v>
+        <v>-47.33714393587855</v>
       </c>
       <c r="F100">
-        <v>-0.6002525630314883</v>
+        <v>-0.7197105978218022</v>
       </c>
       <c r="G100">
-        <v>-3.245613649732256</v>
+        <v>-2.19753134799993</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.83867292970763</v>
       </c>
       <c r="E101">
-        <v>-50.33298195437842</v>
+        <v>-49.43165599814324</v>
       </c>
       <c r="F101">
-        <v>-0.9730361183741274</v>
+        <v>-0.9721265709658535</v>
       </c>
       <c r="G101">
-        <v>-3.340669343801349</v>
+        <v>-2.156924196415229</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.0693993016079</v>
       </c>
       <c r="E102">
-        <v>-53.43360546506027</v>
+        <v>-51.52365475733369</v>
       </c>
       <c r="F102">
-        <v>-1.161804482124079</v>
+        <v>-1.556412205060874</v>
       </c>
       <c r="G102">
-        <v>-3.89115678770798</v>
+        <v>-2.211846146911739</v>
       </c>
     </row>
   </sheetData>
